--- a/technology_surveys/022_lease_digitalization_perception_survey--technology_surveys.xlsx
+++ b/technology_surveys/022_lease_digitalization_perception_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>less_than_6_months</t>
+          <t>less than 6 months</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6_months_to_1_year</t>
+          <t>6 months to 1 year</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1_to_2_years</t>
+          <t>1 to 2 years</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2_to_5_years</t>
+          <t>2 to 5 years</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>more_than_5_years</t>
+          <t>more than 5 years</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>user_experience</t>
+          <t>user experience</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>speed_of_process</t>
+          <t>speed of process</t>
         </is>
       </c>
     </row>
